--- a/data/Taller_DET_Agosto/Carga_ob_640kW/elmo_data.xlsx
+++ b/data/Taller_DET_Agosto/Carga_ob_640kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Taller_DET_Agosto\Carga_ob_640kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC43B4B-F957-4872-994F-F5F9D8013053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C920B1-77C2-49C1-A18F-5CD14B7B0D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2391,8 +2391,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="8">
-        <f>2*35722</f>
-        <v>71444</v>
+        <v>35722</v>
       </c>
       <c r="D3" s="12">
         <v>38221</v>
@@ -2401,13 +2400,13 @@
         <v>5733</v>
       </c>
       <c r="F3" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="8">
         <v>1</v>
       </c>
       <c r="H3" s="8">
-        <v>2400</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
